--- a/backend/excelfiles/QualifyingInterviewScore.xlsx
+++ b/backend/excelfiles/QualifyingInterviewScore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mark\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MIS-USER1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6454CD80-122E-4844-BC1C-805AF616A584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{692D848E-CF53-4046-982F-72BC7529447F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39255" yWindow="5025" windowWidth="14400" windowHeight="7275" xr2:uid="{D641B30A-98F5-42AF-80EE-37A96E8DDEFE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D641B30A-98F5-42AF-80EE-37A96E8DDEFE}"/>
   </bookViews>
   <sheets>
     <sheet name="Qualifying_Exam" sheetId="1" r:id="rId1"/>
@@ -25,21 +25,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Applicant ID</t>
   </si>
   <si>
-    <t>Qualifying Interview Score</t>
-  </si>
-  <si>
     <t>Qualifying Exam Score</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Accepted</t>
+    <t>Qualifying Status</t>
+  </si>
+  <si>
+    <t>Interview Exam Score</t>
+  </si>
+  <si>
+    <t>Interview Status</t>
+  </si>
+  <si>
+    <t>College Status</t>
+  </si>
+  <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>REJECTED</t>
   </si>
 </sst>
 </file>
@@ -75,16 +87,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -104,9 +113,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -144,7 +153,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -250,7 +259,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -392,7 +401,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -400,58 +409,68 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D5C5D3-48C1-41AE-8428-890D0D59BE2D}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.6328125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="43.08984375" customWidth="1"/>
-    <col min="3" max="3" width="23.08984375" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="43.140625" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" customWidth="1"/>
     <col min="4" max="4" width="27" style="1" customWidth="1"/>
-    <col min="5" max="5" width="30.90625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.453125" customWidth="1"/>
+    <col min="5" max="5" width="30.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1"/>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>2026100002</v>
       </c>
       <c r="B2" s="1">
         <v>95</v>
       </c>
-      <c r="C2" s="1">
-        <v>90</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2"/>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1">
+        <v>95</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3"/>
       <c r="D3"/>
       <c r="E3"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4"/>
       <c r="D4"/>
       <c r="E4"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="D5"/>
       <c r="E5"/>
